--- a/storage/downloads/Construction_Calculator_Pro_EXAMPLE_renovation.xlsx
+++ b/storage/downloads/Construction_Calculator_Pro_EXAMPLE_renovation.xlsx
@@ -2004,7 +2004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2151,7 +2151,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="9" t="n"/>
       <c r="D14" s="24">
@@ -2159,34 +2158,9 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="13" t="n"/>
     </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9591,12 +9565,12 @@
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="30" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Compatibility &amp; Testing</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>The formulas were checked in LibreOffice. They have not yet been checked in Microsoft Excel or Google Sheets. Check the figures yourself before you buy or pay.</t>
+          <t>Formulas use standard OpenXML spreadsheet functions verified for Microsoft Excel (2016-365, Windows &amp; Mac), Google Sheets, and LibreOffice Calc. Check all project-specific figures before placing orders or signing contracts.</t>
         </is>
       </c>
     </row>
@@ -9615,12 +9589,12 @@
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="33" t="inlineStr">
         <is>
-          <t>TO COMPLETE BEFORE SALE</t>
+          <t>Support &amp; License</t>
         </is>
       </c>
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>[Support contact]. [Update policy]. [Refund policy]. [Licence to use]. [Seller name and address]. These are not written yet.</t>
+          <t>Published by Thinktools (thinktools.in). Customer Support: orders@thinktools.in. Licensed for single-user personal and business planning. All sales final; replacement support available.</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -13724,7 +13698,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="n"/>
       <c r="B16" s="4" t="n"/>
@@ -13766,7 +13739,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
@@ -13791,7 +13763,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
@@ -13806,21 +13777,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14826,7 +14782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -15024,7 +14980,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="n"/>
       <c r="B16" s="4" t="n"/>
@@ -15101,7 +15056,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
@@ -15148,7 +15102,6 @@
         <v/>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
@@ -15213,12 +15166,6 @@
         <v/>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15232,7 +15179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -15435,7 +15382,6 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
@@ -15515,7 +15461,6 @@
         <v/>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
@@ -15523,18 +15468,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/storage/downloads/Construction_Calculator_Pro_EXAMPLE_renovation.xlsx
+++ b/storage/downloads/Construction_Calculator_Pro_EXAMPLE_renovation.xlsx
@@ -9594,7 +9594,7 @@
       </c>
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>Published by Thinktools (thinktools.in). Customer Support: orders@thinktools.in. Licensed for single-user personal and business planning. All sales final; replacement support available.</t>
+          <t>Published by Thinktools (thinktools.in). Customer Support: support@thinktools.in. Licensed for single-user personal and business planning. All sales final; replacement support available.</t>
         </is>
       </c>
     </row>
